--- a/JNVST_MAT_PDF_Metadata_Template.xlsx
+++ b/JNVST_MAT_PDF_Metadata_Template.xlsx
@@ -10,9 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MAT Metadata" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MAT Metadata'!$A$1:$H$7</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -32,12 +30,17 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -54,7 +57,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,28 +423,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Question No</t>
+          <t>Question_No</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Correct Option</t>
+          <t>Correct_Option</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -456,20 +460,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Variation_Group</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Marks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Cognitive_Level</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Difficulty</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
@@ -494,12 +503,25 @@
           <t>Pattern Completion</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>PAT-001</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>1</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Knowledge</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -520,119 +542,27 @@
           <t>Pattern Completion</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>PAT-001</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>1</v>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>MAT_SERIES</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Figure Series</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>MAT_GEOMETRICAL</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Geometrical Figure Completion</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>MAT_MIRROR</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Mirror &amp; Water Imaging</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>MAT_EMBEDDED</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Embedded Figure</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Application</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -643,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -652,70 +582,42 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>JNVST MAT PDF + Metadata Bulk Upload</t>
+          <t>JNVST MAT PDF Metadata — Variation Group</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Required columns: Question No, Correct Option, Part, Topic, Marks</t>
+          <t>Variation_Group is optional. Use the same group code for similar MAT alternatives.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Question No must match the PDF page number exactly.</t>
+          <t>When the JNVST Question Paper Generator Variation Group Rule is enabled, only one question from a group can be selected.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Part values: MAT_PATTERN, MAT_SERIES, MAT_GEOMETRICAL, MAT_MIRROR, MAT_EMBEDDED</t>
+          <t>Part, Topic and Marks are required.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cognitive_Level is optional: Knowledge, Understanding, Application, HOTS</t>
+          <t>Question_No must match the PDF page number.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Difficulty is optional: Easy, Medium, Hard</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Explanation is optional.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>One PDF page = one image-based MAT question.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Unnecessary white space around each PDF page is cropped automatically.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Each MAT Part must contain a multiple of 4 questions.</t>
+          <t>This metadata is stored in mock_question_bank only; School Course is not affected.</t>
         </is>
       </c>
     </row>

--- a/JNVST_MAT_PDF_Metadata_Template.xlsx
+++ b/JNVST_MAT_PDF_Metadata_Template.xlsx
@@ -10,7 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MAT Metadata" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MAT Metadata'!$A$1:$H$7</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -30,17 +32,12 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -57,7 +54,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -423,29 +420,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Question_No</t>
+          <t>Question No</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Correct_Option</t>
+          <t>Correct Option</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -460,25 +456,20 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Variation_Group</t>
+          <t>Marks</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Marks</t>
+          <t>Cognitive_Level</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Cognitive_Level</t>
+          <t>Difficulty</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Difficulty</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
@@ -503,25 +494,12 @@
           <t>Pattern Completion</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>PAT-001</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
+      <c r="E2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Knowledge</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -542,27 +520,119 @@
           <t>Pattern Completion</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>PAT-001</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
+      <c r="E3" t="n">
         <v>1</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Application</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>MAT_SERIES</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Figure Series</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>MAT_GEOMETRICAL</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Geometrical Figure Completion</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>MAT_MIRROR</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Mirror &amp; Water Imaging</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MAT_EMBEDDED</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Embedded Figure</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -573,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -582,42 +652,70 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>JNVST MAT PDF Metadata — Variation Group</t>
+          <t>JNVST MAT PDF + Metadata Bulk Upload</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Variation_Group is optional. Use the same group code for similar MAT alternatives.</t>
+          <t>Required columns: Question No, Correct Option, Part, Topic, Marks</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>When the JNVST Question Paper Generator Variation Group Rule is enabled, only one question from a group can be selected.</t>
+          <t>Question No must match the PDF page number exactly.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Part, Topic and Marks are required.</t>
+          <t>Part values: MAT_PATTERN, MAT_SERIES, MAT_GEOMETRICAL, MAT_MIRROR, MAT_EMBEDDED</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Question_No must match the PDF page number.</t>
+          <t>Cognitive_Level is optional: Knowledge, Understanding, Application, HOTS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>This metadata is stored in mock_question_bank only; School Course is not affected.</t>
+          <t>Difficulty is optional: Easy, Medium, Hard</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Explanation is optional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>One PDF page = one image-based MAT question.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Unnecessary white space around each PDF page is cropped automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Each MAT Part must contain a multiple of 4 questions.</t>
         </is>
       </c>
     </row>

--- a/JNVST_MAT_PDF_Metadata_Template.xlsx
+++ b/JNVST_MAT_PDF_Metadata_Template.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -430,7 +430,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -471,6 +471,11 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Explanation</t>
         </is>
       </c>
@@ -497,9 +502,11 @@
       <c r="E2" t="n">
         <v>1</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -523,9 +530,11 @@
       <c r="E3" t="n">
         <v>1</v>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -549,9 +558,11 @@
       <c r="E4" t="n">
         <v>1</v>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -575,9 +586,11 @@
       <c r="E5" t="n">
         <v>1</v>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -601,9 +614,11 @@
       <c r="E6" t="n">
         <v>1</v>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -627,9 +642,11 @@
       <c r="E7" t="n">
         <v>1</v>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H7"/>
@@ -643,7 +660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -719,6 +736,13 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Common: write YES for questions frequently asked in exams (any Difficulty level); NO or blank otherwise. Questions in the same Variation Group as a Common question are treated as Common automatically.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
